--- a/reports/빅딜/history/2026-05-18/빅딜_league_mgf_report.xlsx
+++ b/reports/빅딜/history/2026-05-18/빅딜_league_mgf_report.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">빅딜!$A$1:$J$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">빅딜!$A$1:$J$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">슈즈!$A$1:$J$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">장비!$A$1:$J$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">재앙!$A$1:$J$22</definedName>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1458" uniqueCount="516">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1498" uniqueCount="552">
   <si>
     <t>guild_name</t>
   </si>
@@ -230,568 +230,676 @@
     <t>combat_power</t>
   </si>
   <si>
+    <t>1위</t>
+  </si>
+  <si>
+    <t>킹몬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%AA%AC</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>다크나이트</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>127조 4158억 2520만</t>
+  </si>
+  <si>
+    <t>울힝</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B8%ED%9E%9D</t>
+  </si>
+  <si>
+    <t>비숍</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>124조 2857억 5103만</t>
+  </si>
+  <si>
+    <t>3위</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EA%B2%9C%EA%B0%90%EB%B3%84%EC%82%AC</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>71조 1311억 293만</t>
+  </si>
+  <si>
+    <t>4위</t>
+  </si>
+  <si>
+    <t>오티엘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%ED%8B%B0%EC%97%98</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>55조 1697억 241만</t>
+  </si>
+  <si>
+    <t>5위</t>
+  </si>
+  <si>
+    <t>큐샤프</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%81%90%EC%83%A4%ED%94%84</t>
+  </si>
+  <si>
+    <t>신궁</t>
+  </si>
+  <si>
+    <t>47조 1872억 7713만</t>
+  </si>
+  <si>
+    <t>6위</t>
+  </si>
+  <si>
+    <t>엘라임</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%9D%BC%EC%9E%84</t>
+  </si>
+  <si>
+    <t>히어로</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>37조 2025억 1259만</t>
+  </si>
+  <si>
+    <t>익맹</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B5%EB%A7%B9</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>29조 2855억 7714만</t>
+  </si>
+  <si>
+    <t>8위</t>
+  </si>
+  <si>
+    <t>단풍카우</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EC%B9%B4%EC%9A%B0</t>
+  </si>
+  <si>
+    <t>25조 5222억 7641만</t>
+  </si>
+  <si>
+    <t>야가다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EA%B0%80%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>보우마스터</t>
+  </si>
+  <si>
+    <t>18조 6811억 3690만</t>
+  </si>
+  <si>
+    <t>10위</t>
+  </si>
+  <si>
+    <t>아르미느</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EB%AF%B8%EB%8A%90</t>
+  </si>
+  <si>
+    <t>18조 611억 3324만</t>
+  </si>
+  <si>
+    <t>양정팔</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%A0%95%ED%8C%94</t>
+  </si>
+  <si>
+    <t>18조 33억 1513만</t>
+  </si>
+  <si>
+    <t>12위</t>
+  </si>
+  <si>
+    <t>굴러가는일상</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%B4%EB%9F%AC%EA%B0%80%EB%8A%94%EC%9D%BC%EC%83%81</t>
+  </si>
+  <si>
+    <t>아크메이지(썬,콜)</t>
+  </si>
+  <si>
+    <t>17조 2503억 3903만</t>
+  </si>
+  <si>
+    <t>포스코퓨처엠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EC%8A%A4%EC%BD%94%ED%93%A8%EC%B2%98%EC%97%A0</t>
+  </si>
+  <si>
+    <t>섀도어</t>
+  </si>
+  <si>
+    <t>14조 4786억 4858만</t>
+  </si>
+  <si>
+    <t>14위</t>
+  </si>
+  <si>
+    <t>KR#TAKIN9CP37</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=KR%23TAKIN9CP37</t>
+  </si>
+  <si>
+    <t>12조 9889억 8160만</t>
+  </si>
+  <si>
+    <t>15위</t>
+  </si>
+  <si>
+    <t>흑두부</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EB%91%90%EB%B6%80</t>
+  </si>
+  <si>
+    <t>12조 4350억 5906만</t>
+  </si>
+  <si>
+    <t>16위</t>
+  </si>
+  <si>
+    <t>우후</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>12조 3713억 1192만</t>
+  </si>
+  <si>
+    <t>17위</t>
+  </si>
+  <si>
+    <t>비스밤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
+  </si>
+  <si>
+    <t>10조 1633억 6981만</t>
+  </si>
+  <si>
+    <t>18위</t>
+  </si>
+  <si>
+    <t>뻥뻥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BB%A5%EB%BB%A5</t>
+  </si>
+  <si>
+    <t>9조 8104억 260만</t>
+  </si>
+  <si>
+    <t>19위</t>
+  </si>
+  <si>
+    <t>꾸르꾸르</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%A5%B4%EA%BE%B8%EB%A5%B4</t>
+  </si>
+  <si>
+    <t>8조 6441억 726만</t>
+  </si>
+  <si>
+    <t>20위</t>
+  </si>
+  <si>
+    <t>아르젠타</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EC%A0%A0%ED%83%80</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>7조 9942억 9967만</t>
+  </si>
+  <si>
+    <t>21위</t>
+  </si>
+  <si>
+    <t>므고</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AF%80%EA%B3%A0</t>
+  </si>
+  <si>
+    <t>7조 9273억 406만</t>
+  </si>
+  <si>
+    <t>22위</t>
+  </si>
+  <si>
+    <t>민들레꽃</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
+  </si>
+  <si>
+    <t>6조 8368억 7385만</t>
+  </si>
+  <si>
+    <t>23위</t>
+  </si>
+  <si>
+    <t>불보독지</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%EB%B3%B4%EB%8F%85%EC%A7%80</t>
+  </si>
+  <si>
+    <t>아크메이지(불,독)</t>
+  </si>
+  <si>
+    <t>6조 2311억 5403만</t>
+  </si>
+  <si>
+    <t>24위</t>
+  </si>
+  <si>
+    <t>덕르코프</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8D%95%EB%A5%B4%EC%BD%94%ED%94%84</t>
+  </si>
+  <si>
+    <t>5조 3996억 7064만</t>
+  </si>
+  <si>
+    <t>25위</t>
+  </si>
+  <si>
+    <t>플로우00</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%8C%EB%A1%9C%EC%9A%B000</t>
+  </si>
+  <si>
+    <t>4조 9551억 9411만</t>
+  </si>
+  <si>
+    <t>26위</t>
+  </si>
+  <si>
+    <t>제스프리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EC%8A%A4%ED%94%84%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>4조 3416억 2655만</t>
+  </si>
+  <si>
+    <t>27위</t>
+  </si>
+  <si>
+    <t>데드캣</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8D%B0%EB%93%9C%EC%BA%A3</t>
+  </si>
+  <si>
+    <t>3조 4048억 3962만</t>
+  </si>
+  <si>
+    <t>28위</t>
+  </si>
+  <si>
+    <t>자유이용껀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9C%A0%EC%9D%B4%EC%9A%A9%EA%BB%80</t>
+  </si>
+  <si>
+    <t>3조 3267억 9445만</t>
+  </si>
+  <si>
+    <t>29위</t>
+  </si>
+  <si>
+    <t>여눈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%88%88</t>
+  </si>
+  <si>
+    <t>2조 8773억 332만</t>
+  </si>
+  <si>
     <t>1</t>
   </si>
   <si>
-    <t>킹몬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%AA%AC</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>다크나이트</t>
-  </si>
-  <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>127조 4158억 2520만</t>
+    <t>현쓰담</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%84%EC%93%B0%EB%8B%B4</t>
+  </si>
+  <si>
+    <t>168조 1912억 4974만</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>울힝</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B8%ED%9E%9D</t>
-  </si>
-  <si>
-    <t>비숍</t>
-  </si>
-  <si>
-    <t>106</t>
-  </si>
-  <si>
-    <t>124조 2857억 5103만</t>
+    <t>freedill</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=freedill</t>
+  </si>
+  <si>
+    <t>82조 7164억 9662만</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EA%B2%9C%EA%B0%90%EB%B3%84%EC%82%AC</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>71조 1311억 293만</t>
+    <t>신중맨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%EC%A4%91%EB%A7%A8</t>
+  </si>
+  <si>
+    <t>81조 2941억 5058만</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>오티엘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%ED%8B%B0%EC%97%98</t>
-  </si>
-  <si>
-    <t>104</t>
-  </si>
-  <si>
-    <t>55조 1697억 241만</t>
+    <t>떳다뀨뀨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%96%B3%EB%8B%A4%EB%80%A8%EB%80%A8</t>
+  </si>
+  <si>
+    <t>52조 6626억 7679만</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>큐샤프</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%81%90%EC%83%A4%ED%94%84</t>
-  </si>
-  <si>
-    <t>신궁</t>
-  </si>
-  <si>
-    <t>47조 1872억 7713만</t>
+    <t>오늘도레벨업</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EB%8A%98%EB%8F%84%EB%A0%88%EB%B2%A8%EC%97%85</t>
+  </si>
+  <si>
+    <t>30조 9650억 5319만</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>엘라임</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%9D%BC%EC%9E%84</t>
-  </si>
-  <si>
-    <t>히어로</t>
-  </si>
-  <si>
-    <t>103</t>
-  </si>
-  <si>
-    <t>37조 2025억 1259만</t>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EB%8F%8C%EC%87%A0</t>
+  </si>
+  <si>
+    <t>23조 728억 175만</t>
   </si>
   <si>
     <t>7</t>
   </si>
   <si>
-    <t>익맹</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B5%EB%A7%B9</t>
-  </si>
-  <si>
-    <t>102</t>
-  </si>
-  <si>
-    <t>29조 2855억 7714만</t>
+    <t>동현맨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%99%ED%98%84%EB%A7%A8</t>
+  </si>
+  <si>
+    <t>22조 4699억 2872만</t>
   </si>
   <si>
     <t>8</t>
   </si>
   <si>
-    <t>단풍카우</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EC%B9%B4%EC%9A%B0</t>
-  </si>
-  <si>
-    <t>25조 5222억 7641만</t>
+    <t>LoveD</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=LoveD</t>
+  </si>
+  <si>
+    <t>19조 4126억 7070만</t>
   </si>
   <si>
     <t>9</t>
   </si>
   <si>
-    <t>야가다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EA%B0%80%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>보우마스터</t>
-  </si>
-  <si>
-    <t>18조 6811억 3690만</t>
+    <t>슈코미</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%88%EC%BD%94%EB%AF%B8</t>
+  </si>
+  <si>
+    <t>18조 7399억 9348만</t>
   </si>
   <si>
     <t>10</t>
   </si>
   <si>
-    <t>아르미느</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EB%AF%B8%EB%8A%90</t>
-  </si>
-  <si>
-    <t>18조 611억 3324만</t>
+    <t>푸른철</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%91%B8%EB%A5%B8%EC%B2%A0</t>
+  </si>
+  <si>
+    <t>17조 4791억 14만</t>
   </si>
   <si>
     <t>11</t>
   </si>
   <si>
-    <t>양정팔</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%A0%95%ED%8C%94</t>
-  </si>
-  <si>
-    <t>18조 33억 1513만</t>
+    <t>최이도</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EC%9D%B4%EB%8F%84</t>
+  </si>
+  <si>
+    <t>15조 5592억 3567만</t>
   </si>
   <si>
     <t>12</t>
   </si>
   <si>
-    <t>굴러가는일상</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%B4%EB%9F%AC%EA%B0%80%EB%8A%94%EC%9D%BC%EC%83%81</t>
-  </si>
-  <si>
-    <t>아크메이지(썬,콜)</t>
-  </si>
-  <si>
-    <t>17조 2503억 3903만</t>
+    <t>말걸면차단</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EA%B1%B8%EB%A9%B4%EC%B0%A8%EB%8B%A8</t>
+  </si>
+  <si>
+    <t>13조 6087억 7944만</t>
   </si>
   <si>
     <t>13</t>
   </si>
   <si>
-    <t>포스코퓨처엠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EC%8A%A4%EC%BD%94%ED%93%A8%EC%B2%98%EC%97%A0</t>
-  </si>
-  <si>
-    <t>섀도어</t>
-  </si>
-  <si>
-    <t>14조 4786억 4858만</t>
+    <t>흐으르</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9D%90%EC%9C%BC%EB%A5%B4</t>
+  </si>
+  <si>
+    <t>10조 8130억 4377만</t>
   </si>
   <si>
     <t>14</t>
   </si>
   <si>
-    <t>KR#TAKIN9CP37</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=KR%23TAKIN9CP37</t>
-  </si>
-  <si>
-    <t>12조 9889억 8160만</t>
+    <t>규LI</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B7%9CLI</t>
+  </si>
+  <si>
+    <t>10조 6770억 5468만</t>
   </si>
   <si>
     <t>15</t>
   </si>
   <si>
-    <t>흑두부</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EB%91%90%EB%B6%80</t>
-  </si>
-  <si>
-    <t>12조 4350억 5906만</t>
+    <t>체크레이스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B2%B4%ED%81%AC%EB%A0%88%EC%9D%B4%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>나이트로드</t>
+  </si>
+  <si>
+    <t>8조 8764억 6552만</t>
   </si>
   <si>
     <t>16</t>
   </si>
   <si>
-    <t>우후</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
-  </si>
-  <si>
-    <t>101</t>
-  </si>
-  <si>
-    <t>12조 3713억 1192만</t>
+    <t>이너타이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%84%88%ED%83%80%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>6조 8056억 3759만</t>
   </si>
   <si>
     <t>17</t>
   </si>
   <si>
-    <t>비스밤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
-  </si>
-  <si>
-    <t>10조 1633억 6981만</t>
+    <t>유쫑</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%AB%91</t>
+  </si>
+  <si>
+    <t>6조 4380억 8979만</t>
   </si>
   <si>
     <t>18</t>
   </si>
   <si>
-    <t>뻥뻥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BB%A5%EB%BB%A5</t>
-  </si>
-  <si>
-    <t>9조 8104억 260만</t>
+    <t>삘선</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%98%EC%84%A0</t>
+  </si>
+  <si>
+    <t>5조 9328억 1942만</t>
   </si>
   <si>
     <t>19</t>
   </si>
   <si>
-    <t>꾸르꾸르</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%A5%B4%EA%BE%B8%EB%A5%B4</t>
-  </si>
-  <si>
-    <t>8조 6441억 726만</t>
+    <t>말개코</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EA%B0%9C%EC%BD%94</t>
+  </si>
+  <si>
+    <t>5조 8447억 5418만</t>
   </si>
   <si>
     <t>20</t>
   </si>
   <si>
-    <t>므고</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AF%80%EA%B3%A0</t>
-  </si>
-  <si>
-    <t>7조 9273억 406만</t>
+    <t>보마영진이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EB%A7%88%EC%98%81%EC%A7%84%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>5조 8322억 7746만</t>
   </si>
   <si>
     <t>21</t>
   </si>
   <si>
-    <t>민들레꽃</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
-  </si>
-  <si>
-    <t>6조 8368억 7385만</t>
+    <t>김필준</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%95%84%EC%A4%80</t>
+  </si>
+  <si>
+    <t>5조 3464억 329만</t>
   </si>
   <si>
     <t>22</t>
   </si>
   <si>
-    <t>불보독지</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%EB%B3%B4%EB%8F%85%EC%A7%80</t>
-  </si>
-  <si>
-    <t>아크메이지(불,독)</t>
-  </si>
-  <si>
-    <t>6조 2311억 5403만</t>
+    <t>곰뮤리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B0%EB%AE%A4%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>5조 2676억 2174만</t>
   </si>
   <si>
     <t>23</t>
   </si>
   <si>
-    <t>플로우00</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%8C%EB%A1%9C%EC%9A%B000</t>
-  </si>
-  <si>
-    <t>4조 9551억 9411만</t>
+    <t>빅띡</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%85%EB%9D%A1</t>
+  </si>
+  <si>
+    <t>4조 9826억 5547만</t>
   </si>
   <si>
     <t>24</t>
   </si>
   <si>
-    <t>제스프리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EC%8A%A4%ED%94%84%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>4조 3416억 2655만</t>
+    <t>전사웅성</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%84%EC%82%AC%EC%9B%85%EC%84%B1</t>
+  </si>
+  <si>
+    <t>4조 7974억 1766만</t>
   </si>
   <si>
     <t>25</t>
-  </si>
-  <si>
-    <t>데드캣</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8D%B0%EB%93%9C%EC%BA%A3</t>
-  </si>
-  <si>
-    <t>3조 4048억 3962만</t>
-  </si>
-  <si>
-    <t>현쓰담</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%84%EC%93%B0%EB%8B%B4</t>
-  </si>
-  <si>
-    <t>168조 1912억 4974만</t>
-  </si>
-  <si>
-    <t>freedill</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=freedill</t>
-  </si>
-  <si>
-    <t>82조 7164억 9662만</t>
-  </si>
-  <si>
-    <t>신중맨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%EC%A4%91%EB%A7%A8</t>
-  </si>
-  <si>
-    <t>81조 2941억 5058만</t>
-  </si>
-  <si>
-    <t>떳다뀨뀨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%96%B3%EB%8B%A4%EB%80%A8%EB%80%A8</t>
-  </si>
-  <si>
-    <t>52조 6626억 7679만</t>
-  </si>
-  <si>
-    <t>오늘도레벨업</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EB%8A%98%EB%8F%84%EB%A0%88%EB%B2%A8%EC%97%85</t>
-  </si>
-  <si>
-    <t>30조 9650억 5319만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EB%8F%8C%EC%87%A0</t>
-  </si>
-  <si>
-    <t>23조 728억 175만</t>
-  </si>
-  <si>
-    <t>동현맨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%99%ED%98%84%EB%A7%A8</t>
-  </si>
-  <si>
-    <t>22조 4699억 2872만</t>
-  </si>
-  <si>
-    <t>LoveD</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=LoveD</t>
-  </si>
-  <si>
-    <t>19조 4126억 7070만</t>
-  </si>
-  <si>
-    <t>슈코미</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%88%EC%BD%94%EB%AF%B8</t>
-  </si>
-  <si>
-    <t>18조 7399억 9348만</t>
-  </si>
-  <si>
-    <t>푸른철</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%91%B8%EB%A5%B8%EC%B2%A0</t>
-  </si>
-  <si>
-    <t>17조 4791억 14만</t>
-  </si>
-  <si>
-    <t>최이도</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EC%9D%B4%EB%8F%84</t>
-  </si>
-  <si>
-    <t>15조 5592억 3567만</t>
-  </si>
-  <si>
-    <t>말걸면차단</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EA%B1%B8%EB%A9%B4%EC%B0%A8%EB%8B%A8</t>
-  </si>
-  <si>
-    <t>13조 6087억 7944만</t>
-  </si>
-  <si>
-    <t>흐으르</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9D%90%EC%9C%BC%EB%A5%B4</t>
-  </si>
-  <si>
-    <t>10조 8130억 4377만</t>
-  </si>
-  <si>
-    <t>규LI</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B7%9CLI</t>
-  </si>
-  <si>
-    <t>10조 6770억 5468만</t>
-  </si>
-  <si>
-    <t>체크레이스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B2%B4%ED%81%AC%EB%A0%88%EC%9D%B4%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>나이트로드</t>
-  </si>
-  <si>
-    <t>8조 8764억 6552만</t>
-  </si>
-  <si>
-    <t>이너타이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%84%88%ED%83%80%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>6조 8056억 3759만</t>
-  </si>
-  <si>
-    <t>유쫑</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%AB%91</t>
-  </si>
-  <si>
-    <t>6조 4380억 8979만</t>
-  </si>
-  <si>
-    <t>삘선</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%98%EC%84%A0</t>
-  </si>
-  <si>
-    <t>5조 9328억 1942만</t>
-  </si>
-  <si>
-    <t>말개코</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EA%B0%9C%EC%BD%94</t>
-  </si>
-  <si>
-    <t>5조 8447억 5418만</t>
-  </si>
-  <si>
-    <t>보마영진이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EB%A7%88%EC%98%81%EC%A7%84%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>5조 8322억 7746만</t>
-  </si>
-  <si>
-    <t>김필준</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%95%84%EC%A4%80</t>
-  </si>
-  <si>
-    <t>5조 3464억 329만</t>
-  </si>
-  <si>
-    <t>곰뮤리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B0%EB%AE%A4%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>5조 2676억 2174만</t>
-  </si>
-  <si>
-    <t>빅띡</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%85%EB%9D%A1</t>
-  </si>
-  <si>
-    <t>4조 9826억 5547만</t>
-  </si>
-  <si>
-    <t>전사웅성</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%84%EC%82%AC%EC%9B%85%EC%84%B1</t>
-  </si>
-  <si>
-    <t>4조 7974억 1766만</t>
   </si>
   <si>
     <t>경주야</t>
@@ -2214,7 +2322,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -2295,28 +2403,28 @@
         <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>79</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -2327,7 +2435,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>23</v>
@@ -2336,19 +2444,19 @@
         <v>23</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>82</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>83</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -2359,16 +2467,16 @@
         <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>85</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>86</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>70</v>
@@ -2377,10 +2485,10 @@
         <v>71</v>
       </c>
       <c r="H5" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>88</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -2391,28 +2499,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>93</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -2423,28 +2531,28 @@
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G7" s="2" t="s">
+      <c r="H7" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="I7" s="2" t="s">
         <v>98</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>99</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -2455,28 +2563,28 @@
         <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="F8" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="I8" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>104</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -2487,16 +2595,16 @@
         <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>105</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>107</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>70</v>
@@ -2508,7 +2616,7 @@
         <v>72</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -2519,28 +2627,28 @@
         <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="H10" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>110</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>113</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -2551,28 +2659,28 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>114</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>117</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -2583,28 +2691,28 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>118</v>
+        <v>45</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G12" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="H12" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="H12" s="2" t="s">
-        <v>98</v>
-      </c>
       <c r="I12" s="2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -2615,28 +2723,28 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>126</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -2647,28 +2755,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>127</v>
+        <v>36</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -2679,28 +2787,28 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G15" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>130</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>135</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -2711,28 +2819,28 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -2743,28 +2851,28 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -2775,28 +2883,28 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="H18" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>143</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>148</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -2807,28 +2915,28 @@
         <v>13</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -2839,28 +2947,28 @@
         <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -2871,28 +2979,28 @@
         <v>13</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>103</v>
+        <v>155</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -2903,16 +3011,16 @@
         <v>13</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>70</v>
@@ -2921,10 +3029,10 @@
         <v>125</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -2935,28 +3043,28 @@
         <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>168</v>
+        <v>121</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>143</v>
+        <v>101</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -2967,28 +3075,28 @@
         <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>112</v>
+        <v>168</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -2999,28 +3107,28 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>92</v>
+        <v>125</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>177</v>
+        <v>155</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -3031,35 +3139,163 @@
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="D27" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="E26" s="2" t="s">
+      <c r="F27" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="F26" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I26" s="2" t="s">
+      <c r="J27" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="J26" s="2" t="s">
+      <c r="C28" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="J30" s="2" t="s">
         <v>24</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J26"/>
+  <autoFilter ref="A1:J30"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -3086,6 +3322,10 @@
     <hyperlink ref="E24" r:id="rId23"/>
     <hyperlink ref="E25" r:id="rId24"/>
     <hyperlink ref="E26" r:id="rId25"/>
+    <hyperlink ref="E27" r:id="rId26"/>
+    <hyperlink ref="E28" r:id="rId27"/>
+    <hyperlink ref="E29" r:id="rId28"/>
+    <hyperlink ref="E30" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3143,28 +3383,28 @@
         <v>25</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>67</v>
+        <v>194</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="I2" s="2" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -3175,28 +3415,28 @@
         <v>25</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>74</v>
+        <v>198</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -3207,28 +3447,28 @@
         <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>80</v>
+        <v>202</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>72</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -3239,28 +3479,28 @@
         <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>84</v>
+        <v>206</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -3271,28 +3511,28 @@
         <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>89</v>
+        <v>210</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -3303,7 +3543,7 @@
         <v>25</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>94</v>
+        <v>214</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>32</v>
@@ -3312,19 +3552,19 @@
         <v>32</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -3335,28 +3575,28 @@
         <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>100</v>
+        <v>217</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>201</v>
+        <v>219</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>202</v>
+        <v>220</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -3367,28 +3607,28 @@
         <v>25</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>105</v>
+        <v>221</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>203</v>
+        <v>222</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>203</v>
+        <v>222</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>204</v>
+        <v>223</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>205</v>
+        <v>224</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -3399,16 +3639,16 @@
         <v>25</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>109</v>
+        <v>225</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>70</v>
@@ -3417,10 +3657,10 @@
         <v>168</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>208</v>
+        <v>228</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -3431,28 +3671,28 @@
         <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>114</v>
+        <v>229</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>209</v>
+        <v>230</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>209</v>
+        <v>230</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>210</v>
+        <v>231</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>211</v>
+        <v>232</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -3463,28 +3703,28 @@
         <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>118</v>
+        <v>233</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>212</v>
+        <v>234</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>212</v>
+        <v>234</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>213</v>
+        <v>235</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G12" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="H12" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="H12" s="2" t="s">
-        <v>98</v>
-      </c>
       <c r="I12" s="2" t="s">
-        <v>214</v>
+        <v>236</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -3495,28 +3735,28 @@
         <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>122</v>
+        <v>237</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>216</v>
+        <v>239</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -3527,16 +3767,16 @@
         <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>127</v>
+        <v>241</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>218</v>
+        <v>242</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>218</v>
+        <v>242</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>219</v>
+        <v>243</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>70</v>
@@ -3545,10 +3785,10 @@
         <v>71</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>220</v>
+        <v>244</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -3559,28 +3799,28 @@
         <v>25</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>132</v>
+        <v>245</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>221</v>
+        <v>246</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>221</v>
+        <v>246</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>222</v>
+        <v>247</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>223</v>
+        <v>248</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -3591,28 +3831,28 @@
         <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>136</v>
+        <v>249</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>224</v>
+        <v>250</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>224</v>
+        <v>250</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>226</v>
+        <v>252</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>227</v>
+        <v>253</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -3623,16 +3863,16 @@
         <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>140</v>
+        <v>254</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>228</v>
+        <v>255</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>228</v>
+        <v>255</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>229</v>
+        <v>256</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>70</v>
@@ -3641,10 +3881,10 @@
         <v>71</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>230</v>
+        <v>257</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -3655,28 +3895,28 @@
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>145</v>
+        <v>258</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>231</v>
+        <v>259</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>231</v>
+        <v>259</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>232</v>
+        <v>260</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>233</v>
+        <v>261</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -3687,28 +3927,28 @@
         <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>149</v>
+        <v>262</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>234</v>
+        <v>263</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>234</v>
+        <v>263</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>235</v>
+        <v>264</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>236</v>
+        <v>265</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -3719,28 +3959,28 @@
         <v>25</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>153</v>
+        <v>266</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>237</v>
+        <v>267</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>237</v>
+        <v>267</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>238</v>
+        <v>268</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>239</v>
+        <v>269</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -3751,28 +3991,28 @@
         <v>25</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>157</v>
+        <v>270</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>241</v>
+        <v>272</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>242</v>
+        <v>273</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -3783,28 +4023,28 @@
         <v>25</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>161</v>
+        <v>274</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>243</v>
+        <v>275</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>243</v>
+        <v>275</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>244</v>
+        <v>276</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>226</v>
+        <v>252</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>245</v>
+        <v>277</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -3815,28 +4055,28 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>165</v>
+        <v>278</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>246</v>
+        <v>279</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>246</v>
+        <v>279</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>247</v>
+        <v>280</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>248</v>
+        <v>281</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -3847,28 +4087,28 @@
         <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>170</v>
+        <v>282</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>249</v>
+        <v>283</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>249</v>
+        <v>283</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>250</v>
+        <v>284</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>177</v>
+        <v>155</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>251</v>
+        <v>285</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -3879,28 +4119,28 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>174</v>
+        <v>286</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>252</v>
+        <v>287</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>252</v>
+        <v>287</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>253</v>
+        <v>288</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>254</v>
+        <v>289</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -3911,28 +4151,28 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>179</v>
+        <v>290</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>255</v>
+        <v>291</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>255</v>
+        <v>291</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>256</v>
+        <v>292</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>226</v>
+        <v>252</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>257</v>
+        <v>293</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -3943,28 +4183,28 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>258</v>
+        <v>294</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>259</v>
+        <v>295</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>259</v>
+        <v>295</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>260</v>
+        <v>296</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>177</v>
+        <v>155</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>261</v>
+        <v>297</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -3975,28 +4215,28 @@
         <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>262</v>
+        <v>298</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>263</v>
+        <v>299</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>263</v>
+        <v>299</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>264</v>
+        <v>300</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>265</v>
+        <v>301</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -4007,28 +4247,28 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>266</v>
+        <v>302</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>267</v>
+        <v>303</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>267</v>
+        <v>303</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>268</v>
+        <v>304</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>269</v>
+        <v>305</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -4039,28 +4279,28 @@
         <v>25</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>270</v>
+        <v>306</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>271</v>
+        <v>307</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>271</v>
+        <v>307</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>272</v>
+        <v>308</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>177</v>
+        <v>155</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>273</v>
+        <v>309</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -4155,28 +4395,28 @@
         <v>33</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>67</v>
+        <v>194</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>274</v>
+        <v>310</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>274</v>
+        <v>310</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>275</v>
+        <v>311</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="I2" s="2" t="s">
-        <v>276</v>
+        <v>312</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -4187,7 +4427,7 @@
         <v>33</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>74</v>
+        <v>198</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>40</v>
@@ -4196,19 +4436,19 @@
         <v>40</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>277</v>
+        <v>313</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>278</v>
+        <v>314</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>279</v>
+        <v>315</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -4219,28 +4459,28 @@
         <v>33</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>80</v>
+        <v>202</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>280</v>
+        <v>316</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>280</v>
+        <v>316</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>281</v>
+        <v>317</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>282</v>
+        <v>318</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -4251,28 +4491,28 @@
         <v>33</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>84</v>
+        <v>206</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>283</v>
+        <v>319</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>283</v>
+        <v>319</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>284</v>
+        <v>320</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>72</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>285</v>
+        <v>321</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -4283,28 +4523,28 @@
         <v>33</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>89</v>
+        <v>210</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>286</v>
+        <v>322</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>286</v>
+        <v>322</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>287</v>
+        <v>323</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>288</v>
+        <v>324</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -4315,28 +4555,28 @@
         <v>33</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>94</v>
+        <v>214</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>289</v>
+        <v>325</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>289</v>
+        <v>325</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>290</v>
+        <v>326</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>291</v>
+        <v>327</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -4347,28 +4587,28 @@
         <v>33</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>100</v>
+        <v>217</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>292</v>
+        <v>328</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>292</v>
+        <v>328</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>293</v>
+        <v>329</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>294</v>
+        <v>330</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -4379,16 +4619,16 @@
         <v>33</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>105</v>
+        <v>221</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>295</v>
+        <v>331</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>295</v>
+        <v>331</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>296</v>
+        <v>332</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>70</v>
@@ -4397,10 +4637,10 @@
         <v>71</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>297</v>
+        <v>333</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -4411,28 +4651,28 @@
         <v>33</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>109</v>
+        <v>225</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>298</v>
+        <v>334</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>298</v>
+        <v>334</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>299</v>
+        <v>335</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>300</v>
+        <v>336</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -4443,28 +4683,28 @@
         <v>33</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>114</v>
+        <v>229</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>301</v>
+        <v>337</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>301</v>
+        <v>337</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>302</v>
+        <v>338</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>303</v>
+        <v>339</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -4475,16 +4715,16 @@
         <v>33</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>118</v>
+        <v>233</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>304</v>
+        <v>340</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>304</v>
+        <v>340</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>305</v>
+        <v>341</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>70</v>
@@ -4493,10 +4733,10 @@
         <v>71</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>306</v>
+        <v>342</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -4507,16 +4747,16 @@
         <v>33</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>122</v>
+        <v>237</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>307</v>
+        <v>343</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>307</v>
+        <v>343</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>308</v>
+        <v>344</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>70</v>
@@ -4525,10 +4765,10 @@
         <v>168</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>309</v>
+        <v>345</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -4539,28 +4779,28 @@
         <v>33</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>127</v>
+        <v>241</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>310</v>
+        <v>346</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>310</v>
+        <v>346</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>311</v>
+        <v>347</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>312</v>
+        <v>348</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -4571,28 +4811,28 @@
         <v>33</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>132</v>
+        <v>245</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>313</v>
+        <v>349</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>313</v>
+        <v>349</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>314</v>
+        <v>350</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>315</v>
+        <v>351</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -4603,28 +4843,28 @@
         <v>33</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>136</v>
+        <v>249</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>316</v>
+        <v>352</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>316</v>
+        <v>352</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>317</v>
+        <v>353</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>318</v>
+        <v>354</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -4635,16 +4875,16 @@
         <v>33</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>140</v>
+        <v>254</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>319</v>
+        <v>355</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>319</v>
+        <v>355</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>320</v>
+        <v>356</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>70</v>
@@ -4653,10 +4893,10 @@
         <v>168</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>321</v>
+        <v>357</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -4667,28 +4907,28 @@
         <v>33</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>145</v>
+        <v>258</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>322</v>
+        <v>358</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>322</v>
+        <v>358</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>323</v>
+        <v>359</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>324</v>
+        <v>360</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -4699,28 +4939,28 @@
         <v>33</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>149</v>
+        <v>262</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>325</v>
+        <v>361</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>325</v>
+        <v>361</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>326</v>
+        <v>362</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>327</v>
+        <v>363</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -4731,28 +4971,28 @@
         <v>33</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>153</v>
+        <v>266</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>329</v>
+        <v>365</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>330</v>
+        <v>366</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -4763,28 +5003,28 @@
         <v>33</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>157</v>
+        <v>270</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>331</v>
+        <v>367</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>331</v>
+        <v>367</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>332</v>
+        <v>368</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>333</v>
+        <v>369</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -4795,28 +5035,28 @@
         <v>33</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>161</v>
+        <v>274</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>334</v>
+        <v>370</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>334</v>
+        <v>370</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>335</v>
+        <v>371</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>226</v>
+        <v>252</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>177</v>
+        <v>155</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>336</v>
+        <v>372</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -4903,28 +5143,28 @@
         <v>41</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>67</v>
+        <v>194</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>337</v>
+        <v>373</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>337</v>
+        <v>373</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>338</v>
+        <v>374</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>278</v>
+        <v>314</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>339</v>
+        <v>375</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -4935,28 +5175,28 @@
         <v>41</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>74</v>
+        <v>198</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>340</v>
+        <v>376</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>340</v>
+        <v>376</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>341</v>
+        <v>377</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>342</v>
+        <v>378</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -4967,28 +5207,28 @@
         <v>41</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>80</v>
+        <v>202</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>343</v>
+        <v>379</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>343</v>
+        <v>379</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>344</v>
+        <v>380</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>345</v>
+        <v>381</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -4999,28 +5239,28 @@
         <v>41</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>84</v>
+        <v>206</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>346</v>
+        <v>382</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>346</v>
+        <v>382</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>347</v>
+        <v>383</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>348</v>
+        <v>384</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -5031,28 +5271,28 @@
         <v>41</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>89</v>
+        <v>210</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>349</v>
+        <v>385</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>349</v>
+        <v>385</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>350</v>
+        <v>386</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>351</v>
+        <v>387</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -5063,28 +5303,28 @@
         <v>41</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>94</v>
+        <v>214</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>352</v>
+        <v>388</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>352</v>
+        <v>388</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>353</v>
+        <v>389</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>354</v>
+        <v>390</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -5095,28 +5335,28 @@
         <v>41</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>100</v>
+        <v>217</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>355</v>
+        <v>391</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>355</v>
+        <v>391</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>356</v>
+        <v>392</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>357</v>
+        <v>393</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -5127,28 +5367,28 @@
         <v>41</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>105</v>
+        <v>221</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>358</v>
+        <v>394</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>358</v>
+        <v>394</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>359</v>
+        <v>395</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>360</v>
+        <v>396</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -5159,28 +5399,28 @@
         <v>41</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>109</v>
+        <v>225</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>361</v>
+        <v>397</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>361</v>
+        <v>397</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>362</v>
+        <v>398</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>226</v>
+        <v>252</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>363</v>
+        <v>399</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -5191,28 +5431,28 @@
         <v>41</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>114</v>
+        <v>229</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>364</v>
+        <v>400</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>364</v>
+        <v>400</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>365</v>
+        <v>401</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>226</v>
+        <v>252</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>366</v>
+        <v>402</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -5223,28 +5463,28 @@
         <v>41</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>118</v>
+        <v>233</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>367</v>
+        <v>403</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>367</v>
+        <v>403</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>368</v>
+        <v>404</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>369</v>
+        <v>405</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -5255,28 +5495,28 @@
         <v>41</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>122</v>
+        <v>237</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>370</v>
+        <v>406</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>370</v>
+        <v>406</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>371</v>
+        <v>407</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>372</v>
+        <v>408</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -5287,28 +5527,28 @@
         <v>41</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>127</v>
+        <v>241</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>373</v>
+        <v>409</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>373</v>
+        <v>409</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>374</v>
+        <v>410</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>375</v>
+        <v>411</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -5319,28 +5559,28 @@
         <v>41</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>132</v>
+        <v>245</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>376</v>
+        <v>412</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>376</v>
+        <v>412</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>377</v>
+        <v>413</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>226</v>
+        <v>252</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>177</v>
+        <v>155</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>378</v>
+        <v>414</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -5351,28 +5591,28 @@
         <v>41</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>136</v>
+        <v>249</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>379</v>
+        <v>415</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>379</v>
+        <v>415</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>380</v>
+        <v>416</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>177</v>
+        <v>155</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>381</v>
+        <v>417</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -5383,16 +5623,16 @@
         <v>41</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>140</v>
+        <v>254</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>382</v>
+        <v>418</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>382</v>
+        <v>418</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>383</v>
+        <v>419</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>70</v>
@@ -5401,10 +5641,10 @@
         <v>168</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>384</v>
+        <v>420</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -5415,28 +5655,28 @@
         <v>41</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>145</v>
+        <v>258</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>385</v>
+        <v>421</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>385</v>
+        <v>421</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>386</v>
+        <v>422</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>387</v>
+        <v>423</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -5447,28 +5687,28 @@
         <v>41</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>149</v>
+        <v>262</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>388</v>
+        <v>424</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>388</v>
+        <v>424</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>389</v>
+        <v>425</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>226</v>
+        <v>252</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>177</v>
+        <v>155</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>390</v>
+        <v>426</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -5479,16 +5719,16 @@
         <v>41</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>153</v>
+        <v>266</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>391</v>
+        <v>427</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>391</v>
+        <v>427</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>392</v>
+        <v>428</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>70</v>
@@ -5497,10 +5737,10 @@
         <v>168</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>393</v>
+        <v>429</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -5511,28 +5751,28 @@
         <v>41</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>157</v>
+        <v>270</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>394</v>
+        <v>430</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>394</v>
+        <v>430</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>395</v>
+        <v>431</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>226</v>
+        <v>252</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>396</v>
+        <v>432</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -5543,28 +5783,28 @@
         <v>41</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>161</v>
+        <v>274</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>397</v>
+        <v>433</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>397</v>
+        <v>433</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>398</v>
+        <v>434</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>399</v>
+        <v>435</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>400</v>
+        <v>436</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -5575,16 +5815,16 @@
         <v>41</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>165</v>
+        <v>278</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>401</v>
+        <v>437</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>401</v>
+        <v>437</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>402</v>
+        <v>438</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>70</v>
@@ -5593,10 +5833,10 @@
         <v>168</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>177</v>
+        <v>155</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>403</v>
+        <v>439</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -5607,28 +5847,28 @@
         <v>41</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>170</v>
+        <v>282</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>404</v>
+        <v>440</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>404</v>
+        <v>440</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>405</v>
+        <v>441</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>177</v>
+        <v>155</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>406</v>
+        <v>442</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -5639,28 +5879,28 @@
         <v>41</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>174</v>
+        <v>286</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>407</v>
+        <v>443</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>407</v>
+        <v>443</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>408</v>
+        <v>444</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>177</v>
+        <v>155</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>409</v>
+        <v>445</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -5671,28 +5911,28 @@
         <v>41</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>179</v>
+        <v>290</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>410</v>
+        <v>446</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>410</v>
+        <v>446</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>411</v>
+        <v>447</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>177</v>
+        <v>155</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>412</v>
+        <v>448</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -5703,7 +5943,7 @@
         <v>41</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>258</v>
+        <v>294</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>49</v>
@@ -5712,19 +5952,19 @@
         <v>49</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>413</v>
+        <v>449</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>177</v>
+        <v>155</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>414</v>
+        <v>450</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -5735,28 +5975,28 @@
         <v>41</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>262</v>
+        <v>298</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>415</v>
+        <v>451</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>415</v>
+        <v>451</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>416</v>
+        <v>452</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>399</v>
+        <v>435</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>417</v>
+        <v>453</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -5767,28 +6007,28 @@
         <v>41</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>266</v>
+        <v>302</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>418</v>
+        <v>454</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>418</v>
+        <v>454</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>419</v>
+        <v>455</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>420</v>
+        <v>456</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>421</v>
+        <v>457</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -5882,28 +6122,28 @@
         <v>50</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>67</v>
+        <v>194</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>422</v>
+        <v>458</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>422</v>
+        <v>458</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>423</v>
+        <v>459</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>424</v>
+        <v>460</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -5914,28 +6154,28 @@
         <v>50</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>74</v>
+        <v>198</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>425</v>
+        <v>461</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>425</v>
+        <v>461</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>426</v>
+        <v>462</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>427</v>
+        <v>463</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -5946,28 +6186,28 @@
         <v>50</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>80</v>
+        <v>202</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>428</v>
+        <v>464</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>428</v>
+        <v>464</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>429</v>
+        <v>465</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>430</v>
+        <v>466</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -5978,28 +6218,28 @@
         <v>50</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>84</v>
+        <v>206</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>431</v>
+        <v>467</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>431</v>
+        <v>467</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>432</v>
+        <v>468</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>433</v>
+        <v>469</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -6010,16 +6250,16 @@
         <v>50</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>89</v>
+        <v>210</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>434</v>
+        <v>470</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>434</v>
+        <v>470</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>435</v>
+        <v>471</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>70</v>
@@ -6028,10 +6268,10 @@
         <v>71</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>436</v>
+        <v>472</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -6042,28 +6282,28 @@
         <v>50</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>94</v>
+        <v>214</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>437</v>
+        <v>473</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>437</v>
+        <v>473</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>438</v>
+        <v>474</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>439</v>
+        <v>475</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -6074,28 +6314,28 @@
         <v>50</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>100</v>
+        <v>217</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>440</v>
+        <v>476</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>440</v>
+        <v>476</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>441</v>
+        <v>477</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>442</v>
+        <v>478</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -6106,28 +6346,28 @@
         <v>50</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>105</v>
+        <v>221</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>444</v>
+        <v>480</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>445</v>
+        <v>481</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -6138,28 +6378,28 @@
         <v>50</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>109</v>
+        <v>225</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>446</v>
+        <v>482</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>446</v>
+        <v>482</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>447</v>
+        <v>483</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>448</v>
+        <v>484</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -6170,28 +6410,28 @@
         <v>50</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>114</v>
+        <v>229</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>449</v>
+        <v>485</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>449</v>
+        <v>485</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>450</v>
+        <v>486</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>177</v>
+        <v>155</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>451</v>
+        <v>487</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -6202,28 +6442,28 @@
         <v>50</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>118</v>
+        <v>233</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>452</v>
+        <v>488</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>452</v>
+        <v>488</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>453</v>
+        <v>489</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>177</v>
+        <v>155</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>454</v>
+        <v>490</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -6234,28 +6474,28 @@
         <v>50</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>122</v>
+        <v>237</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>455</v>
+        <v>491</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>455</v>
+        <v>491</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>456</v>
+        <v>492</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>399</v>
+        <v>435</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>457</v>
+        <v>493</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -6266,28 +6506,28 @@
         <v>50</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>127</v>
+        <v>241</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>458</v>
+        <v>494</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>458</v>
+        <v>494</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>459</v>
+        <v>495</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>177</v>
+        <v>155</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>460</v>
+        <v>496</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -6298,28 +6538,28 @@
         <v>50</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>132</v>
+        <v>245</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>461</v>
+        <v>497</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>461</v>
+        <v>497</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>462</v>
+        <v>498</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>177</v>
+        <v>155</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>463</v>
+        <v>499</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -6330,28 +6570,28 @@
         <v>50</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>136</v>
+        <v>249</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>464</v>
+        <v>500</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>464</v>
+        <v>500</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>465</v>
+        <v>501</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>466</v>
+        <v>502</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>467</v>
+        <v>503</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -6362,28 +6602,28 @@
         <v>50</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>140</v>
+        <v>254</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>468</v>
+        <v>504</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>468</v>
+        <v>504</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>469</v>
+        <v>505</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>177</v>
+        <v>155</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>470</v>
+        <v>506</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -6394,28 +6634,28 @@
         <v>50</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>145</v>
+        <v>258</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>471</v>
+        <v>507</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>471</v>
+        <v>507</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>472</v>
+        <v>508</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>466</v>
+        <v>502</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>473</v>
+        <v>509</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -6426,28 +6666,28 @@
         <v>50</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>149</v>
+        <v>262</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>474</v>
+        <v>510</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>474</v>
+        <v>510</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>475</v>
+        <v>511</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>466</v>
+        <v>502</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>476</v>
+        <v>512</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -6458,28 +6698,28 @@
         <v>50</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>153</v>
+        <v>266</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>477</v>
+        <v>513</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>477</v>
+        <v>513</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>478</v>
+        <v>514</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>479</v>
+        <v>515</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>480</v>
+        <v>516</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -6490,28 +6730,28 @@
         <v>50</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>157</v>
+        <v>270</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>481</v>
+        <v>517</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>481</v>
+        <v>517</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>482</v>
+        <v>518</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>483</v>
+        <v>519</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>484</v>
+        <v>520</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -6522,28 +6762,28 @@
         <v>50</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>161</v>
+        <v>274</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>485</v>
+        <v>521</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>485</v>
+        <v>521</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>486</v>
+        <v>522</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>483</v>
+        <v>519</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>487</v>
+        <v>523</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -6554,28 +6794,28 @@
         <v>50</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>165</v>
+        <v>278</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>488</v>
+        <v>524</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>488</v>
+        <v>524</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>489</v>
+        <v>525</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>483</v>
+        <v>519</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>490</v>
+        <v>526</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -6586,28 +6826,28 @@
         <v>50</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>170</v>
+        <v>282</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>491</v>
+        <v>527</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>491</v>
+        <v>527</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>492</v>
+        <v>528</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>226</v>
+        <v>252</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>493</v>
+        <v>529</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>494</v>
+        <v>530</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -6618,28 +6858,28 @@
         <v>50</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>174</v>
+        <v>286</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>495</v>
+        <v>531</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>495</v>
+        <v>531</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>496</v>
+        <v>532</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>493</v>
+        <v>529</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>497</v>
+        <v>533</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -6650,28 +6890,28 @@
         <v>50</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>179</v>
+        <v>290</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>498</v>
+        <v>534</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>498</v>
+        <v>534</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>499</v>
+        <v>535</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>493</v>
+        <v>529</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>500</v>
+        <v>536</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -6682,7 +6922,7 @@
         <v>50</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>258</v>
+        <v>294</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>58</v>
@@ -6691,19 +6931,19 @@
         <v>58</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>501</v>
+        <v>537</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>483</v>
+        <v>519</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>502</v>
+        <v>538</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -6714,28 +6954,28 @@
         <v>50</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>262</v>
+        <v>298</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>503</v>
+        <v>539</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>503</v>
+        <v>539</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>504</v>
+        <v>540</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>420</v>
+        <v>456</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>505</v>
+        <v>541</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -6746,28 +6986,28 @@
         <v>50</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>266</v>
+        <v>302</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>506</v>
+        <v>542</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>506</v>
+        <v>542</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>507</v>
+        <v>543</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>493</v>
+        <v>529</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>508</v>
+        <v>544</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -6778,28 +7018,28 @@
         <v>50</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>270</v>
+        <v>306</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>509</v>
+        <v>545</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>509</v>
+        <v>545</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>510</v>
+        <v>546</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>493</v>
+        <v>529</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>511</v>
+        <v>547</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -6810,16 +7050,16 @@
         <v>50</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>512</v>
+        <v>548</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>513</v>
+        <v>549</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>513</v>
+        <v>549</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>514</v>
+        <v>550</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>70</v>
@@ -6828,10 +7068,10 @@
         <v>71</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>420</v>
+        <v>456</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>515</v>
+        <v>551</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
